--- a/Dữ liệu Đơn hàng.xlsx
+++ b/Dữ liệu Đơn hàng.xlsx
@@ -1,155 +1,223 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HK2Nam2\PTTKHTTT\DoAn\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE72994-E69A-40F6-AD2E-A3BFD047FF51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Ghi Chú Khách Hàng Đặt Máy Tính" sheetId="1" r:id="rId5"/>
+    <sheet name="Cập Nhật Đơn Hàng Và Lưu Ý" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
-  <si>
-    <t>Mã HĐ</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="57">
+  <si>
+    <t>Mã Đơn Hàng</t>
+  </si>
+  <si>
+    <t>Ngày Đặt</t>
   </si>
   <si>
     <t>Khách Hàng</t>
   </si>
   <si>
-    <t>Sản Phẩm</t>
+    <t>Phương Thức Thanh Toán</t>
   </si>
   <si>
     <t>Ghi Chú Của Khách Hàng</t>
   </si>
   <si>
-    <t>HD1001</t>
+    <t>DH001</t>
   </si>
   <si>
     <t>Trần Thị Mai Chi</t>
   </si>
   <si>
-    <t>Acer Nitro V ANV15</t>
+    <t>Chuyển khoản</t>
   </si>
   <si>
     <t>"Giao hàng sau 5 giờ chiều vì giờ hành chính tôi đi làm."</t>
   </si>
   <si>
-    <t>HD1002</t>
+    <t>DH002</t>
   </si>
   <si>
     <t>Lê Hoàng Nam</t>
   </si>
   <si>
-    <t>Asus ROG Strix G16 2024</t>
-  </si>
-  <si>
-    <t>"Máy dùng làm đồ họa, nhờ kỹ thuật kiểm tra kỹ màn hình xem có hở sáng không."</t>
-  </si>
-  <si>
-    <t>HD1003</t>
+    <t>"Máy dùng làm đồ họa, nhờ kỹ thuật kiểm tra kỹ màn hình."</t>
+  </si>
+  <si>
+    <t>DH003</t>
   </si>
   <si>
     <t>Nguyễn Văn Tú</t>
   </si>
   <si>
-    <t>"Cài giúp tôi bộ phần mềm Adobe (Photoshop, Premiere) trước khi giao."</t>
-  </si>
-  <si>
-    <t>HD1004</t>
+    <t>Tiền mặt</t>
+  </si>
+  <si>
+    <t>"Cài giúp tôi bộ phần mềm Adobe trước khi giao."</t>
+  </si>
+  <si>
+    <t>DH004</t>
+  </si>
+  <si>
+    <t>13/03/2026</t>
   </si>
   <si>
     <t>Phạm Minh Anh</t>
   </si>
   <si>
-    <t>MacBook Air 13 M3</t>
-  </si>
-  <si>
     <t>"Gói quà giúp mình, mình mua tặng sinh nhật em gái."</t>
   </si>
   <si>
-    <t>HD1005</t>
+    <t>DH005</t>
+  </si>
+  <si>
+    <t>14/03/2026</t>
   </si>
   <si>
     <t>Bùi Phương Linh</t>
   </si>
   <si>
-    <t>Dell Inspiron 15 3530</t>
-  </si>
-  <si>
     <t>"Cần gấp trong sáng nay để kịp đi công tác."</t>
   </si>
   <si>
-    <t>HD1006</t>
+    <t>DH006</t>
+  </si>
+  <si>
+    <t>15/03/2026</t>
   </si>
   <si>
     <t>Đặng Thu Thảo</t>
   </si>
   <si>
-    <t>Asus Vivobook 15 X1504</t>
-  </si>
-  <si>
     <t>"Hỗ trợ chia ổ cứng làm 2 phân vùng (C và D) giúp tôi."</t>
   </si>
   <si>
-    <t>HD1007</t>
+    <t>DH007</t>
+  </si>
+  <si>
+    <t>16/03/2026</t>
+  </si>
+  <si>
+    <t>Ngô Quốc Bảo</t>
+  </si>
+  <si>
+    <t>"Liên hệ số điện thoại phụ nếu số chính không gọi được."</t>
+  </si>
+  <si>
+    <t>DH008</t>
   </si>
   <si>
     <t>Vũ Đức Trọng</t>
   </si>
   <si>
-    <t>MSI Katana 15 B13V</t>
-  </si>
-  <si>
-    <t>"Liên hệ số điện thoại phụ 090xxxxxxx nếu số chính không gọi được."</t>
-  </si>
-  <si>
-    <t>HD1008</t>
-  </si>
-  <si>
-    <t>Ngô Quốc Bảo</t>
-  </si>
-  <si>
-    <t>Dell XPS 13 9340</t>
-  </si>
-  <si>
-    <t>"Tôi muốn thanh toán bằng hình thức quẹt thẻ khi nhận hàng."</t>
-  </si>
-  <si>
-    <t>HD1009</t>
-  </si>
-  <si>
-    <t>HP Victus 16 2024</t>
-  </si>
-  <si>
-    <t>"Dán giúp mình miếng dán bảo vệ màn hình và mặt lưng máy."</t>
-  </si>
-  <si>
-    <t>HD1010</t>
-  </si>
-  <si>
-    <t>HP Pavilion 14 dv2000</t>
-  </si>
-  <si>
-    <t>"Nâng cấp thêm 1 thanh RAM 8GB (tổng cộng 16GB) luôn nhé."</t>
+    <t>"Giao đến văn phòng công ty, gọi trước 15 phút."</t>
+  </si>
+  <si>
+    <t>DH009</t>
+  </si>
+  <si>
+    <t>"Xuất hóa đơn đỏ (VAT) cho công ty."</t>
+  </si>
+  <si>
+    <t>DH010</t>
+  </si>
+  <si>
+    <t>17/03/2026</t>
+  </si>
+  <si>
+    <t>"Tặng kèm túi chống sốc như đã hứa nhé shop."</t>
+  </si>
+  <si>
+    <t>DH011</t>
+  </si>
+  <si>
+    <t>"Kiểm tra kỹ sạc và phụ kiện đi kèm."</t>
+  </si>
+  <si>
+    <t>DH012</t>
+  </si>
+  <si>
+    <t>18/03/2026</t>
+  </si>
+  <si>
+    <t>"Cần cài thêm phần mềm AutoCAD 2024."</t>
+  </si>
+  <si>
+    <t>DH013</t>
+  </si>
+  <si>
+    <t>"Giao hàng vào sáng thứ 7 giúp mình."</t>
+  </si>
+  <si>
+    <t>DH014</t>
+  </si>
+  <si>
+    <t>19/03/2026</t>
+  </si>
+  <si>
+    <t>"Máy này mua cho sinh viên, nhờ cài các IDE lập trình."</t>
+  </si>
+  <si>
+    <t>DH015</t>
+  </si>
+  <si>
+    <t>"Màu bạc (Silver) nhé, đừng lấy màu xám."</t>
+  </si>
+  <si>
+    <t>DH016</t>
+  </si>
+  <si>
+    <t>20/03/2026</t>
+  </si>
+  <si>
+    <t>"Thanh toán tiền mặt khi nhận hàng."</t>
+  </si>
+  <si>
+    <t>DH017</t>
+  </si>
+  <si>
+    <t>"Đổi sang mẫu 16GB RAM nếu có sẵn hàng."</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -158,40 +226,65 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
-    <border/>
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -381,17 +474,27 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="50.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -404,13 +507,16 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2">
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="B2" s="2">
+        <v>46298</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>
@@ -418,134 +524,283 @@
       <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3">
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1" t="s">
         <v>9</v>
+      </c>
+      <c r="B3" s="2">
+        <v>46329</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2">
+        <v>46359</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5">
+      <c r="E4" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="1" t="s">
+      <c r="D16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>40</v>
+      <c r="D18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>